--- a/output/pdf_financials_xlsx/LOD.xlsx
+++ b/output/pdf_financials_xlsx/LOD.xlsx
@@ -1168,22 +1168,22 @@
         <v>-0.578162</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>0.092234</v>
+        <v>-0.092234</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>1.132907</v>
+        <v>-1.132907</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>0.544079</v>
+        <v>-0.544079</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>0.316168</v>
+        <v>-0.316168</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>0.253465</v>
+        <v>-0.253465</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>1.520274</v>
+        <v>-1.520274</v>
       </c>
       <c r="K16" s="3" t="n">
         <v>-1.639253</v>
@@ -1210,7 +1210,7 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>-0.147146</v>
+        <v>-2.128474</v>
       </c>
       <c r="C17" s="3" t="n">
         <v>-0.025097</v>
@@ -1415,7 +1415,7 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>0.990664</v>
+        <v>-0.990664</v>
       </c>
       <c r="C20" s="3" t="n">
         <v>-0.78285</v>
@@ -1424,22 +1424,22 @@
         <v>-0.6379280000000001</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>0.092234</v>
+        <v>-0.092234</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>1.132907</v>
+        <v>-1.132907</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>0.544079</v>
+        <v>-0.544079</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>0.316168</v>
+        <v>-0.316168</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>0.253465</v>
+        <v>-0.253465</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>1.520274</v>
+        <v>-1.520274</v>
       </c>
       <c r="K20" s="3" t="n">
         <v>-1.639253</v>
@@ -1568,7 +1568,7 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>0.990664</v>
+        <v>-0.990664</v>
       </c>
       <c r="C23" s="3" t="n">
         <v>-0.78285</v>
@@ -1577,22 +1577,22 @@
         <v>-0.6379280000000001</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>0.092234</v>
+        <v>-0.092234</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>1.132907</v>
+        <v>-1.132907</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>0.544079</v>
+        <v>-0.544079</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>0.316168</v>
+        <v>-0.316168</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>0.253465</v>
+        <v>-0.253465</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>1.520274</v>
+        <v>-1.520274</v>
       </c>
       <c r="K23" s="3" t="n">
         <v>-1.639253</v>
@@ -1739,7 +1739,7 @@
         </is>
       </c>
       <c r="F26" s="3" t="n">
-        <v>87.146692</v>
+        <v>-87.146692</v>
       </c>
       <c r="G26" s="1" t="inlineStr">
         <is>
@@ -1757,7 +1757,7 @@
         </is>
       </c>
       <c r="J26" s="3" t="n">
-        <v>50.6758</v>
+        <v>-50.6758</v>
       </c>
       <c r="K26" s="1" t="inlineStr">
         <is>
@@ -1795,22 +1795,22 @@
         <v>-0.578162</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>0.092234</v>
+        <v>-0.092234</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>1.132907</v>
+        <v>-1.132907</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>0.544079</v>
+        <v>-0.544079</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>0.316168</v>
+        <v>-0.316168</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>0.253465</v>
+        <v>-0.253465</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>1.520274</v>
+        <v>-1.520274</v>
       </c>
       <c r="K27" s="3" t="n">
         <v>-1.639253</v>
@@ -1897,22 +1897,22 @@
         <v>-0.578162</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>0.092234</v>
+        <v>-0.092234</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>1.132907</v>
+        <v>-1.132907</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>0.544079</v>
+        <v>-0.544079</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>0.316168</v>
+        <v>-0.316168</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>0.253465</v>
+        <v>-0.253465</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>1.520274</v>
+        <v>-1.520274</v>
       </c>
       <c r="K29" s="3" t="n">
         <v>-1.639253</v>
@@ -2016,7 +2016,7 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>12.93238765699018</v>
+        <v>187.0676123430098</v>
       </c>
       <c r="C31" s="3" t="n">
         <v>-4.007895379829413</v>
@@ -2025,22 +2025,22 @@
         <v>-10.33724111927107</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K31" s="3" t="n">
         <v>-0</v>
@@ -5334,7 +5334,7 @@
         </is>
       </c>
       <c r="B99" s="3" t="n">
-        <v>0.990664</v>
+        <v>-0.990664</v>
       </c>
       <c r="C99" s="3" t="n">
         <v>-0.795963</v>
@@ -6265,7 +6265,7 @@
         </is>
       </c>
       <c r="B118" s="3" t="n">
-        <v>0</v>
+        <v>-1.515655</v>
       </c>
       <c r="C118" s="3" t="n">
         <v>-0.20724</v>
@@ -35910,7 +35910,11 @@
           <t>Exploration and evaluation expenditures</t>
         </is>
       </c>
-      <c r="D337" t="inlineStr"/>
+      <c r="D337" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E337" s="5" t="n">
         <v>-1.515655</v>
       </c>
@@ -43442,7 +43446,7 @@
         </is>
       </c>
       <c r="M425" s="5" t="n">
-        <v>1.520274</v>
+        <v>-1.520274</v>
       </c>
       <c r="N425" s="5" t="n">
         <v>-1.708253</v>
@@ -47128,10 +47132,10 @@
         </is>
       </c>
       <c r="M468" s="5" t="n">
-        <v>1.520274</v>
+        <v>-1.520274</v>
       </c>
       <c r="N468" s="5" t="n">
-        <v>1.639253</v>
+        <v>-1.639253</v>
       </c>
       <c r="O468" t="inlineStr">
         <is>
@@ -49859,10 +49863,10 @@
         </is>
       </c>
       <c r="L500" s="5" t="n">
-        <v>0.253465</v>
+        <v>-0.253465</v>
       </c>
       <c r="M500" s="5" t="n">
-        <v>1.520274</v>
+        <v>-1.520274</v>
       </c>
       <c r="N500" t="inlineStr">
         <is>
@@ -52480,16 +52484,16 @@
         </is>
       </c>
       <c r="I531" s="5" t="n">
-        <v>1.132907</v>
+        <v>-1.132907</v>
       </c>
       <c r="J531" s="5" t="n">
-        <v>0.544079</v>
+        <v>-0.544079</v>
       </c>
       <c r="K531" s="5" t="n">
-        <v>0.316168</v>
+        <v>-0.316168</v>
       </c>
       <c r="L531" s="5" t="n">
-        <v>0.253465</v>
+        <v>-0.253465</v>
       </c>
       <c r="M531" t="inlineStr">
         <is>
@@ -53921,10 +53925,10 @@
         </is>
       </c>
       <c r="H548" s="5" t="n">
-        <v>0.092234</v>
+        <v>-0.092234</v>
       </c>
       <c r="I548" s="5" t="n">
-        <v>1.132907</v>
+        <v>-1.132907</v>
       </c>
       <c r="J548" t="inlineStr">
         <is>
@@ -56576,10 +56580,10 @@
         </is>
       </c>
       <c r="E579" s="5" t="n">
-        <v>0.990664</v>
+        <v>-0.990664</v>
       </c>
       <c r="F579" s="5" t="n">
-        <v>0.78285</v>
+        <v>-0.78285</v>
       </c>
       <c r="G579" t="inlineStr">
         <is>
@@ -56748,10 +56752,10 @@
         </is>
       </c>
       <c r="E581" s="5" t="n">
-        <v>0.931265</v>
+        <v>-0.931265</v>
       </c>
       <c r="F581" s="5" t="n">
-        <v>0.795963</v>
+        <v>-0.795963</v>
       </c>
       <c r="G581" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/LOD.xlsx
+++ b/output/pdf_financials_xlsx/LOD.xlsx
@@ -862,34 +862,34 @@
         <v>0.15443</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>0</v>
+        <v>0.092234</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>0</v>
+        <v>1.132907</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>0</v>
+        <v>0.499079</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>0</v>
+        <v>0.306168</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>0</v>
+        <v>0.474737</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>0</v>
+        <v>1.604385</v>
       </c>
       <c r="K10" s="3" t="n">
-        <v>0</v>
+        <v>1.804453</v>
       </c>
       <c r="L10" s="3" t="n">
-        <v>0</v>
+        <v>2.945056</v>
       </c>
       <c r="M10" s="3" t="n">
-        <v>0</v>
+        <v>2.088379</v>
       </c>
       <c r="N10" s="3" t="n">
-        <v>0</v>
+        <v>3.979574</v>
       </c>
       <c r="O10" s="1" t="inlineStr">
         <is>
@@ -913,7 +913,7 @@
         <v>-0.423732</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>0</v>
+        <v>-0.092234</v>
       </c>
       <c r="F11" s="3" t="n">
         <v>1.132907</v>
@@ -934,13 +934,13 @@
         <v>1.804453</v>
       </c>
       <c r="L11" s="3" t="n">
-        <v>0</v>
+        <v>-2.945056</v>
       </c>
       <c r="M11" s="3" t="n">
-        <v>0</v>
+        <v>-2.088379</v>
       </c>
       <c r="N11" s="3" t="n">
-        <v>0</v>
+        <v>-3.979574</v>
       </c>
       <c r="O11" s="1" t="inlineStr">
         <is>
@@ -955,13 +955,13 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.004134</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.006828</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.000776</v>
       </c>
       <c r="E12" s="3" t="n">
         <v>0</v>
@@ -1786,13 +1786,13 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>1.13781</v>
+        <v>1.133676</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-0.626189</v>
+        <v>-0.6330170000000001</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-0.578162</v>
+        <v>-0.578938</v>
       </c>
       <c r="E27" s="3" t="n">
         <v>-0.092234</v>
@@ -1888,13 +1888,13 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>1.13781</v>
+        <v>1.133676</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-0.626189</v>
+        <v>-0.6330170000000001</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-0.578162</v>
+        <v>-0.578938</v>
       </c>
       <c r="E29" s="3" t="n">
         <v>-0.092234</v>
@@ -2154,43 +2154,43 @@
         <v>0.491762</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.006432</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.119579</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.053828</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.006164</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.046364</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.377657</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.026076</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>2.97357</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>2.661825</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>1.369179</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>0.023638</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>0.309182</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>0.173815</v>
       </c>
     </row>
     <row r="35">
@@ -2252,43 +2252,43 @@
         <v>0.491762</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.006432</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.119579</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.053828</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.006164</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0.035</v>
+        <v>0.08136400000000001</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0.06</v>
+        <v>0.437657</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0.036</v>
+        <v>0.062076</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0.108</v>
+        <v>3.08157</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0.108</v>
+        <v>2.769825</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0.036</v>
+        <v>1.405179</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0.018</v>
+        <v>0.041638</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0.018</v>
+        <v>0.327182</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0.018</v>
+        <v>0.191815</v>
       </c>
     </row>
     <row r="37">
@@ -2840,43 +2840,43 @@
         <v>0.02</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.059578</v>
+        <v>0.053146</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.220469</v>
+        <v>0.10089</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.053828</v>
+        <v>0</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.007904</v>
+        <v>0.00174</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.046364</v>
+        <v>0</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.387307</v>
+        <v>0.009650000000000001</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.079627</v>
+        <v>0.053551</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>5.908262</v>
+        <v>2.934692</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>4.52634</v>
+        <v>1.864515</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>1.626534</v>
+        <v>0.257355</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>0.202197</v>
+        <v>0.178559</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>0.845596</v>
+        <v>0.5364139999999999</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>0.413501</v>
+        <v>0.239686</v>
       </c>
     </row>
     <row r="49">
@@ -7378,7 +7378,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -14126,7 +14126,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -16918,7 +16918,7 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
@@ -39994,7 +39994,7 @@
       </c>
       <c r="D385" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E385" t="inlineStr">
@@ -42808,7 +42808,7 @@
       </c>
       <c r="D418" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E418" t="inlineStr">
@@ -52130,7 +52130,7 @@
       </c>
       <c r="D527" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E527" t="inlineStr">
@@ -53818,7 +53818,7 @@
       </c>
       <c r="D547" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E547" t="inlineStr">
@@ -54338,7 +54338,7 @@
       </c>
       <c r="D553" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E553" t="inlineStr">
@@ -55542,7 +55542,7 @@
       </c>
       <c r="D567" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E567" s="5" t="n">

--- a/output/pdf_financials_xlsx/LOD.xlsx
+++ b/output/pdf_financials_xlsx/LOD.xlsx
@@ -5885,16 +5885,16 @@
         <v>0</v>
       </c>
       <c r="F110" s="3" t="n">
-        <v>0</v>
+        <v>0.034235</v>
       </c>
       <c r="G110" s="3" t="n">
-        <v>0</v>
+        <v>0.040413</v>
       </c>
       <c r="H110" s="3" t="n">
-        <v>0</v>
+        <v>0.01803</v>
       </c>
       <c r="I110" s="3" t="n">
-        <v>0</v>
+        <v>0.00197</v>
       </c>
       <c r="J110" s="3" t="n">
         <v>0</v>
@@ -21000,7 +21000,11 @@
           <t>Proceeds from share issuances (Note 9)</t>
         </is>
       </c>
-      <c r="D162" t="inlineStr"/>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E162" t="inlineStr">
         <is>
           <t>-</t>
@@ -23898,7 +23902,11 @@
           <t>Proceeds from shares issuances (Note 11)</t>
         </is>
       </c>
-      <c r="D196" t="inlineStr"/>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E196" t="inlineStr">
         <is>
           <t>-</t>
@@ -25536,7 +25544,11 @@
           <t>Proceeds from share issuances (Note 11)</t>
         </is>
       </c>
-      <c r="D215" t="inlineStr"/>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E215" t="inlineStr">
         <is>
           <t>-</t>
@@ -27574,7 +27586,11 @@
           <t>Proceeds from share issuances (Note 12)</t>
         </is>
       </c>
-      <c r="D239" t="inlineStr"/>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E239" t="inlineStr">
         <is>
           <t>-</t>
@@ -30834,7 +30850,11 @@
           <t>Interest and accretion expense (Note 9)</t>
         </is>
       </c>
-      <c r="D277" t="inlineStr"/>
+      <c r="D277" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E277" t="inlineStr">
         <is>
           <t>-</t>
@@ -31400,7 +31420,11 @@
           <t>Proceeds from share issuances (Note 12)</t>
         </is>
       </c>
-      <c r="D284" t="inlineStr"/>
+      <c r="D284" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E284" t="inlineStr">
         <is>
           <t>-</t>
@@ -32304,7 +32328,11 @@
           <t>Interest and accretion expense (Note 10, Note 11)</t>
         </is>
       </c>
-      <c r="D295" t="inlineStr"/>
+      <c r="D295" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E295" t="inlineStr">
         <is>
           <t>-</t>
@@ -33068,7 +33096,11 @@
           <t>Proceeds from share issuances (Note 14)</t>
         </is>
       </c>
-      <c r="D304" t="inlineStr"/>
+      <c r="D304" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E304" t="inlineStr">
         <is>
           <t>-</t>
@@ -33236,7 +33268,11 @@
           <t>Interest and accretion expense (Notes 9 and 10)</t>
         </is>
       </c>
-      <c r="D306" t="inlineStr"/>
+      <c r="D306" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E306" t="inlineStr">
         <is>
           <t>-</t>
@@ -33494,7 +33530,11 @@
           <t>Proceeds from share issuances (Note 13)</t>
         </is>
       </c>
-      <c r="D309" t="inlineStr"/>
+      <c r="D309" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E309" t="inlineStr">
         <is>
           <t>-</t>
@@ -36250,7 +36290,11 @@
           <t>Proceeds from share issuance</t>
         </is>
       </c>
-      <c r="D341" t="inlineStr"/>
+      <c r="D341" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E341" s="5" t="n">
         <v>1.532688</v>
       </c>
